--- a/evaluation_forms/018_medical_wearable_technology_pilot_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/018_medical_wearable_technology_pilot_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -861,8 +861,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -890,12 +890,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'medical_wearable_device_1'}</t>
+          <t>medical_wearable_device_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Medical Wearable Device 1'}</t>
+          <t>Medical Wearable Device 1</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medical_wearable_device_2'}</t>
+          <t>medical_wearable_device_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Medical Wearable Device 2'}</t>
+          <t>Medical Wearable Device 2</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'participant_1'}</t>
+          <t>participant_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Participant 1'}</t>
+          <t>Participant 1</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'participant_2'}</t>
+          <t>participant_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Participant 2'}</t>
+          <t>Participant 2</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'participant_3'}</t>
+          <t>participant_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Participant 3'}</t>
+          <t>Participant 3</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
